--- a/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>DBGI</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -736,44 +737,47 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E8" s="3">
         <v>4500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3400</v>
       </c>
       <c r="G8" s="3">
         <v>3400</v>
       </c>
       <c r="H8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I8" s="3">
         <v>2600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -789,43 +793,46 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2700</v>
       </c>
-      <c r="G9" s="3">
-        <v>1800</v>
-      </c>
       <c r="H9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I9" s="3">
         <v>1500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
-      </c>
-      <c r="L9" s="3">
-        <v>600</v>
       </c>
       <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
+      <c r="N9" s="3">
+        <v>600</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
@@ -842,44 +849,47 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="G10" s="3">
-        <v>1600</v>
-      </c>
       <c r="H10" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I10" s="3">
         <v>1100</v>
       </c>
       <c r="J10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K10" s="3">
         <v>1500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-200</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -895,8 +905,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -916,8 +929,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -969,8 +983,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1022,8 +1039,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,26 +1053,26 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>15500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1066,8 +1086,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1075,19 +1095,22 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>700</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>500</v>
       </c>
       <c r="G15" s="3">
         <v>500</v>
@@ -1099,20 +1122,20 @@
         <v>500</v>
       </c>
       <c r="J15" s="3">
+        <v>500</v>
+      </c>
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,8 +1151,11 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1146,44 +1172,45 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E17" s="3">
         <v>-3100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16600</v>
       </c>
-      <c r="G17" s="3">
-        <v>6000</v>
-      </c>
       <c r="H17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I17" s="3">
         <v>13300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2800</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1199,44 +1226,47 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
         <v>7600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1252,8 +1282,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1273,43 +1306,44 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1326,44 +1360,47 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E21" s="3">
         <v>8400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-2100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,44 +1416,47 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1600</v>
       </c>
       <c r="J22" s="3">
         <v>1600</v>
       </c>
       <c r="K22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1432,44 +1472,47 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
         <v>6500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-4900</v>
-      </c>
       <c r="H23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-9500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1485,8 +1528,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1515,13 +1561,13 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-1100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1532,14 +1578,17 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1591,44 +1640,47 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>6500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-4900</v>
-      </c>
       <c r="H26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-9500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,44 +1696,47 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>6500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15800</v>
       </c>
-      <c r="G27" s="3">
-        <v>-4900</v>
-      </c>
       <c r="H27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-9500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,8 +1752,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1750,34 +1808,37 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1803,8 +1864,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1856,8 +1920,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1909,43 +1976,46 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1962,44 +2032,47 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>5000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2015,8 +2088,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2068,44 +2144,47 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>5000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,49 +2200,52 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2179,8 +2261,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2200,8 +2285,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2221,44 +2307,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2274,8 +2361,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2327,44 +2417,47 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2380,44 +2473,47 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E44" s="3">
         <v>4800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2433,44 +2529,47 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>900</v>
       </c>
       <c r="G45" s="3">
         <v>900</v>
       </c>
       <c r="H45" s="3">
+        <v>900</v>
+      </c>
+      <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2486,44 +2585,47 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2539,8 +2641,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2551,10 +2656,10 @@
         <v>100</v>
       </c>
       <c r="F47" s="3">
+        <v>100</v>
+      </c>
+      <c r="G47" s="3">
         <v>200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
@@ -2566,16 +2671,16 @@
         <v>100</v>
       </c>
       <c r="K47" s="3">
+        <v>100</v>
+      </c>
+      <c r="L47" s="3">
         <v>200</v>
-      </c>
-      <c r="L47" s="3">
-        <v>100</v>
       </c>
       <c r="M47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>100</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2592,31 +2697,34 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
       </c>
       <c r="H48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3">
         <v>300</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -2627,8 +2735,8 @@
       <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>100</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2645,44 +2753,47 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E49" s="3">
         <v>20400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>29500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>30000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>30600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>31100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>34600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>27300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13900</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,8 +2809,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2751,8 +2865,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2804,8 +2921,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2815,11 +2935,11 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>400</v>
@@ -2834,14 +2954,14 @@
         <v>400</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2977,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2910,44 +3033,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E54" s="3">
         <v>27600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2963,8 +3089,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2984,8 +3113,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3005,44 +3135,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E57" s="3">
         <v>8100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3058,8 +3189,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3067,35 +3201,35 @@
         <v>6900</v>
       </c>
       <c r="E58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F58" s="3">
         <v>12500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3111,44 +3245,47 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E59" s="3">
         <v>7600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3164,44 +3301,47 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E60" s="3">
         <v>22700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,44 +3357,47 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>800</v>
-      </c>
-      <c r="F61" s="3">
-        <v>300</v>
       </c>
       <c r="G61" s="3">
         <v>300</v>
       </c>
       <c r="H61" s="3">
+        <v>300</v>
+      </c>
+      <c r="I61" s="3">
         <v>6300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3270,8 +3413,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3279,34 +3425,34 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>1700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3323,8 +3469,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3376,8 +3525,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3429,8 +3581,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3482,44 +3637,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E66" s="3">
         <v>23100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,8 +3693,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3556,8 +3717,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3609,8 +3771,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3662,8 +3827,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3715,8 +3883,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3768,44 +3939,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-110300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-104800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-109900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-103700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-88000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-83100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-73500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-65700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-56000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-47100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3821,8 +3995,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3874,8 +4051,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3927,8 +4107,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3980,44 +4163,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-7900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-7500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-12500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-14900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-13600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-7100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-8900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4033,8 +4219,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4086,49 +4275,52 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4144,44 +4336,47 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>5000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,8 +4392,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4218,19 +4416,20 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
@@ -4245,17 +4444,17 @@
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4271,8 +4470,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4324,8 +4526,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4377,8 +4582,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4430,8 +4638,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4483,8 +4694,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4536,44 +4750,47 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4589,8 +4806,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4610,8 +4830,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4642,8 +4863,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4657,14 +4878,17 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4716,8 +4940,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4769,8 +4996,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4778,14 +5008,14 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7300</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -4793,19 +5023,19 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4816,14 +5046,17 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4843,8 +5076,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4896,8 +5130,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4949,8 +5186,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5002,8 +5242,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5055,44 +5298,47 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5108,8 +5354,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5161,44 +5410,47 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5212,6 +5464,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>DBGI</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -740,50 +741,56 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F8" s="3">
         <v>3300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -796,50 +803,56 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F9" s="3">
         <v>1600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -852,8 +865,14 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,41 +880,41 @@
         <v>1700</v>
       </c>
       <c r="E10" s="3">
+        <v>500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-200</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -908,8 +927,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,8 +955,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,8 +1013,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1042,8 +1075,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1056,29 +1095,29 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>15500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1089,34 +1128,40 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>700</v>
+      </c>
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
@@ -1125,23 +1170,23 @@
         <v>500</v>
       </c>
       <c r="K15" s="3">
+        <v>500</v>
+      </c>
+      <c r="L15" s="3">
+        <v>500</v>
+      </c>
+      <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1199,14 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,50 +1224,52 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>-3100</v>
       </c>
-      <c r="F17" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I17" s="3">
         <v>16600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>13300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>13800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>10100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2800</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,50 +1282,56 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>7600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-13200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-7900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-10800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1285,8 +1344,14 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1307,49 +1372,51 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="M20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1363,50 +1430,56 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>8400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-12300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-7500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-8100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-10700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2200</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,50 +1492,56 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>600</v>
+      </c>
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>3000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>2200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1475,50 +1554,56 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>6500</v>
       </c>
-      <c r="F23" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-15800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-9500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-9700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-11800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1531,16 +1616,22 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1564,16 +1655,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1581,14 +1672,20 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1643,50 +1740,56 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>6500</v>
       </c>
-      <c r="F26" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-15800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-9500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-8900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-10700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,50 +1802,56 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>6500</v>
       </c>
-      <c r="F27" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-15800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-7800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-8900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1864,14 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1926,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1820,31 +1941,31 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-1500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
+        <v>100</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1867,8 +1988,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1923,8 +2050,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1979,49 +2112,55 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="M32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>600</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>700</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="L32" s="3">
-        <v>600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -2035,50 +2174,56 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-6100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-15800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-7800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-8900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2091,8 +2236,14 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2147,50 +2298,56 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-6100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-15800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-7800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-8900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,55 +2360,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2264,8 +2427,14 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2286,8 +2455,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2308,50 +2479,52 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>1100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2537,14 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2420,28 +2599,34 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1500</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1100</v>
       </c>
       <c r="J43" s="3">
         <v>1000</v>
@@ -2450,20 +2635,20 @@
         <v>1100</v>
       </c>
       <c r="L43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2476,50 +2661,56 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="E44" s="3">
         <v>4800</v>
       </c>
       <c r="F44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H44" s="3">
         <v>4900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>600</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2532,50 +2723,56 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1100</v>
       </c>
       <c r="G45" s="3">
         <v>900</v>
       </c>
       <c r="H45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
+        <v>900</v>
+      </c>
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,50 +2785,56 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F46" s="3">
         <v>7700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1700</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,8 +2847,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2659,13 +2868,13 @@
         <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
       </c>
       <c r="I47" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J47" s="3">
         <v>100</v>
@@ -2674,19 +2883,19 @@
         <v>100</v>
       </c>
       <c r="L47" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M47" s="3">
         <v>100</v>
       </c>
       <c r="N47" s="3">
+        <v>200</v>
+      </c>
+      <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>100</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2700,37 +2909,43 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>100</v>
@@ -2738,11 +2953,11 @@
       <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>100</v>
+      </c>
+      <c r="P48" s="3">
+        <v>100</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2756,50 +2971,56 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F49" s="3">
         <v>19700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>20400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>23600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>24500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>29500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>30000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>30600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>31100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>34600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>27300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>13900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2812,8 +3033,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2868,8 +3095,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2924,28 +3157,34 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
         <v>400</v>
@@ -2957,16 +3196,16 @@
         <v>400</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>400</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -2980,8 +3219,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3036,50 +3281,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25300</v>
+      </c>
+      <c r="F54" s="3">
         <v>27700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>27600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>33100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>33700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>35000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>36000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>40700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>34000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>16200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3343,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3114,8 +3371,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3136,50 +3395,52 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F57" s="3">
         <v>8300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>8100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>7700</v>
       </c>
       <c r="G57" s="3">
         <v>8100</v>
       </c>
       <c r="H57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J57" s="3">
         <v>6900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3192,50 +3453,56 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F58" s="3">
         <v>6900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>6900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>12500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>13800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>13200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>11500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>13700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>12400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3248,50 +3515,56 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F59" s="3">
         <v>7200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>20000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>19000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>25400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>25500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>18700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>16100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>9400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,50 +3577,56 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F60" s="3">
         <v>22400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>22700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>40100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>40900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>45500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>44000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>40800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>35000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>23700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>21600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>15400</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3360,8 +3639,14 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3369,41 +3654,41 @@
         <v>200</v>
       </c>
       <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
+        <v>200</v>
+      </c>
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>13000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3416,49 +3701,55 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>1700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3472,8 +3763,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3528,8 +3825,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3584,8 +3887,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3640,50 +3949,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F66" s="3">
         <v>22500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>23100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>41000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>41200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>47500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>51300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>49600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>43600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>39200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>29100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>25000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +4011,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3718,8 +4039,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3774,8 +4097,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3830,8 +4159,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3886,8 +4221,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3942,50 +4283,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-114700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-110300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-104800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-109900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-103700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-88000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-83100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-73500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-65700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-56000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-47100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-36400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4345,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4054,8 +4407,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4110,8 +4469,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4166,50 +4531,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F76" s="3">
         <v>5200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-7900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-7500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-12500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-14900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-13600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-7100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-8900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,8 +4593,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4278,55 +4655,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4339,50 +4722,56 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-6100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-15800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-7800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-8900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4395,8 +4784,14 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4417,8 +4812,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4429,13 +4826,13 @@
         <v>800</v>
       </c>
       <c r="F83" s="3">
+        <v>700</v>
+      </c>
+      <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
         <v>1000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
@@ -4447,20 +4844,20 @@
         <v>600</v>
       </c>
       <c r="L83" s="3">
+        <v>600</v>
+      </c>
+      <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4473,8 +4870,14 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4529,8 +4932,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4585,8 +4994,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4641,8 +5056,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4697,8 +5118,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4753,50 +5180,56 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4809,8 +5242,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4831,8 +5270,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4866,11 +5307,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4881,14 +5322,20 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,8 +5390,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,8 +5452,14 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5011,37 +5470,37 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-7300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="L94" s="3">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>-500</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+        <v>-5000</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5049,14 +5508,20 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5077,8 +5542,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5133,8 +5600,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5189,8 +5662,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5245,8 +5724,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5301,50 +5786,56 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F100" s="3">
         <v>4200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>10300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>6200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>6100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>8800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5848,14 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5413,50 +5910,56 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-1600</v>
+        <v>-1100</v>
       </c>
       <c r="F102" s="3">
         <v>700</v>
       </c>
       <c r="G102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H102" s="3">
+        <v>700</v>
+      </c>
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,6 +5970,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>DBGI</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,53 +748,56 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,52 +813,55 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E9" s="3">
         <v>1900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
-      </c>
-      <c r="O9" s="3">
-        <v>600</v>
       </c>
       <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="Q9" s="3">
+        <v>600</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
@@ -871,53 +878,56 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1100</v>
       </c>
       <c r="L10" s="3">
         <v>1100</v>
       </c>
       <c r="M10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N10" s="3">
         <v>1500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-200</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +970,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,8 +1098,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,26 +1121,26 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>15500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1134,8 +1154,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1143,28 +1163,31 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="E15" s="3">
         <v>700</v>
       </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="G15" s="3">
+        <v>700</v>
+      </c>
+      <c r="H15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
@@ -1176,20 +1199,20 @@
         <v>500</v>
       </c>
       <c r="M15" s="3">
+        <v>500</v>
+      </c>
+      <c r="N15" s="3">
         <v>600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1205,8 +1228,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,53 +1252,54 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>-3100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2800</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,53 +1315,56 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,8 +1407,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1386,40 +1420,40 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1436,53 +1470,56 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,53 +1535,56 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1600</v>
       </c>
       <c r="M22" s="3">
         <v>1600</v>
       </c>
       <c r="N22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1560,53 +1600,56 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,20 +1665,23 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1661,13 +1707,13 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-1100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1678,14 +1724,17 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,53 +1795,56 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,53 +1860,56 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1947,28 +2008,28 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-1500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>100</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="J29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K29" s="3">
         <v>-200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1994,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,8 +2185,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2130,40 +2200,40 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2180,53 +2250,56 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,53 +2380,56 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,58 +2445,61 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,53 +2567,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2630,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2605,8 +2695,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2614,44 +2707,44 @@
         <v>1000</v>
       </c>
       <c r="E43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2667,53 +2760,56 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E44" s="3">
         <v>4600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,53 +2825,56 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
         <v>300</v>
       </c>
       <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>900</v>
       </c>
       <c r="J45" s="3">
         <v>900</v>
       </c>
       <c r="K45" s="3">
+        <v>900</v>
+      </c>
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,53 +2890,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E46" s="3">
         <v>6000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1700</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,13 +2955,16 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
@@ -2874,10 +2979,10 @@
         <v>100</v>
       </c>
       <c r="I47" s="3">
+        <v>100</v>
+      </c>
+      <c r="J47" s="3">
         <v>200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>100</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
@@ -2889,16 +2994,16 @@
         <v>100</v>
       </c>
       <c r="N47" s="3">
+        <v>100</v>
+      </c>
+      <c r="O47" s="3">
         <v>200</v>
-      </c>
-      <c r="O47" s="3">
-        <v>100</v>
       </c>
       <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>100</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2915,40 +3020,43 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>200</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
       </c>
       <c r="K48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>300</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
@@ -2959,8 +3067,8 @@
       <c r="P48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>100</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -2977,53 +3085,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E49" s="3">
         <v>18200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>30000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>30600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>31100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>34600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13900</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3039,8 +3150,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,19 +3280,22 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -3183,11 +3303,11 @@
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>400</v>
@@ -3202,14 +3322,14 @@
         <v>400</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3345,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,53 +3410,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E54" s="3">
         <v>24800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>40700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,53 +3527,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,53 +3590,56 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>6900</v>
       </c>
       <c r="G58" s="3">
         <v>6900</v>
       </c>
       <c r="H58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I58" s="3">
         <v>12500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,53 +3655,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
         <v>7600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,8 +3720,11 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3592,44 +3732,44 @@
         <v>21400</v>
       </c>
       <c r="E60" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F60" s="3">
         <v>23200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>45500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>44000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3785,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3660,38 +3803,38 @@
         <v>200</v>
       </c>
       <c r="G61" s="3">
+        <v>200</v>
+      </c>
+      <c r="H61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
-      </c>
-      <c r="I61" s="3">
-        <v>300</v>
       </c>
       <c r="J61" s="3">
         <v>300</v>
       </c>
       <c r="K61" s="3">
+        <v>300</v>
+      </c>
+      <c r="L61" s="3">
         <v>6300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3707,52 +3850,55 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>1700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3769,8 +3915,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,53 +4110,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E66" s="3">
         <v>21900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>49600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>43600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,53 +4460,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-118200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-114700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-114000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-110300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-104800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-109900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-103700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-88000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-83100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-73500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-65700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-56000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-47100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,53 +4720,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-7900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-7500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-12500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-14900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-13600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-7100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,58 +4850,61 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,53 +4920,56 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,8 +5012,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4823,19 +5022,19 @@
         <v>700</v>
       </c>
       <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
@@ -4850,17 +5049,17 @@
         <v>600</v>
       </c>
       <c r="N83" s="3">
+        <v>600</v>
+      </c>
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4876,8 +5075,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,53 +5400,56 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,8 +5492,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5313,8 +5534,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5328,14 +5549,17 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,13 +5685,16 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -5476,14 +5706,14 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7300</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
@@ -5491,19 +5721,19 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5514,14 +5744,17 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +5777,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5606,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,53 +6035,56 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6100,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5916,53 +6165,56 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6228,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
   <si>
     <t>DBGI</t>
   </si>
@@ -656,86 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -751,56 +752,59 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,55 +820,58 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1000</v>
-      </c>
-      <c r="P9" s="3">
-        <v>600</v>
       </c>
       <c r="Q9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
+      <c r="R9" s="3">
+        <v>600</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
@@ -881,56 +888,59 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1100</v>
       </c>
       <c r="M10" s="3">
         <v>1100</v>
       </c>
       <c r="N10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O10" s="3">
         <v>1500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-200</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -946,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -971,8 +984,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1036,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1101,13 +1118,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>600</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1115,35 +1135,35 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>15500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1157,8 +1177,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1166,31 +1186,34 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
+      <c r="F15" s="3">
+        <v>700</v>
       </c>
       <c r="G15" s="3">
+        <v>800</v>
+      </c>
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1202,20 +1225,20 @@
         <v>500</v>
       </c>
       <c r="N15" s="3">
+        <v>500</v>
+      </c>
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,8 +1254,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1253,56 +1279,57 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E17" s="3">
         <v>5700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
-        <v>-3100</v>
-      </c>
       <c r="I17" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J17" s="3">
         <v>8100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2800</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,56 +1345,59 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3400</v>
       </c>
-      <c r="H18" s="3">
-        <v>7600</v>
-      </c>
       <c r="I18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-3700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1408,13 +1441,14 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1423,40 +1457,40 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>700</v>
+      </c>
+      <c r="K20" s="3">
+        <v>400</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="M20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
-        <v>400</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>3400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1473,8 +1507,11 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1482,47 +1519,47 @@
         <v>-1600</v>
       </c>
       <c r="E21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="F21" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-2800</v>
       </c>
-      <c r="H21" s="3">
-        <v>8400</v>
-      </c>
       <c r="I21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1538,56 +1575,59 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1600</v>
       </c>
       <c r="N22" s="3">
         <v>1600</v>
       </c>
       <c r="O22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1603,8 +1643,11 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1612,47 +1655,47 @@
         <v>-3500</v>
       </c>
       <c r="E23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,8 +1711,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1679,20 +1725,20 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1710,13 +1756,13 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1727,14 +1773,17 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1798,8 +1847,11 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1807,47 +1859,47 @@
         <v>-3500</v>
       </c>
       <c r="E26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,8 +1915,11 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1872,47 +1927,47 @@
         <v>-3500</v>
       </c>
       <c r="E27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5400</v>
       </c>
-      <c r="H27" s="3">
-        <v>6500</v>
-      </c>
       <c r="I27" s="3">
-        <v>-6200</v>
+        <v>5000</v>
       </c>
       <c r="J27" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-15800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1928,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1993,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2011,28 +2072,28 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-1500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>100</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2058,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2123,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2188,13 +2255,16 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2203,40 +2273,40 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="M32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>700</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="O32" s="3">
-        <v>600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2253,8 +2323,11 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2262,47 +2335,47 @@
         <v>-3500</v>
       </c>
       <c r="E33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2318,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2383,8 +2459,11 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2392,47 +2471,47 @@
         <v>-3500</v>
       </c>
       <c r="E35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,61 +2527,64 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2518,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2543,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2568,56 +2654,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
         <v>0</v>
       </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2633,8 +2720,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2698,56 +2788,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
         <v>1000</v>
       </c>
       <c r="F43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,56 +2856,59 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>600</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2828,56 +2924,59 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>900</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>900</v>
       </c>
       <c r="L45" s="3">
+        <v>900</v>
+      </c>
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,56 +2992,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E46" s="3">
         <v>6600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1700</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,34 +3060,37 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>200</v>
-      </c>
-      <c r="K47" s="3">
-        <v>100</v>
       </c>
       <c r="L47" s="3">
         <v>100</v>
@@ -2997,16 +3102,16 @@
         <v>100</v>
       </c>
       <c r="O47" s="3">
+        <v>100</v>
+      </c>
+      <c r="P47" s="3">
         <v>200</v>
-      </c>
-      <c r="P47" s="3">
-        <v>100</v>
       </c>
       <c r="Q47" s="3">
         <v>100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>100</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3023,43 +3128,46 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
       </c>
       <c r="L48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
       </c>
       <c r="N48" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>100</v>
@@ -3070,8 +3178,8 @@
       <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>100</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3088,56 +3196,59 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E49" s="3">
         <v>17500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>30000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>30600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>31100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>34600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>27300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13900</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3153,8 +3264,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3218,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3283,34 +3400,37 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>200</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
@@ -3325,14 +3445,14 @@
         <v>400</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,8 +3468,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3413,56 +3536,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E54" s="3">
         <v>24900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3478,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3503,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3528,56 +3658,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>6100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,56 +3724,59 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6900</v>
+        <v>8900</v>
       </c>
       <c r="E58" s="3">
-        <v>7500</v>
+        <v>8400</v>
       </c>
       <c r="F58" s="3">
-        <v>7300</v>
+        <v>8900</v>
       </c>
       <c r="G58" s="3">
-        <v>6900</v>
+        <v>8500</v>
       </c>
       <c r="H58" s="3">
-        <v>6900</v>
+        <v>7400</v>
       </c>
       <c r="I58" s="3">
-        <v>12500</v>
+        <v>7200</v>
       </c>
       <c r="J58" s="3">
+        <v>13400</v>
+      </c>
+      <c r="K58" s="3">
         <v>13800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,56 +3792,59 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8400</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>7600</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>8400</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>7200</v>
+        <v>400</v>
       </c>
       <c r="H59" s="3">
-        <v>7600</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>20000</v>
+        <v>700</v>
       </c>
       <c r="J59" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K59" s="3">
         <v>19000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,56 +3860,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>21400</v>
+        <v>22400</v>
       </c>
       <c r="E60" s="3">
         <v>21400</v>
       </c>
       <c r="F60" s="3">
+        <v>21400</v>
+      </c>
+      <c r="G60" s="3">
         <v>23200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>44000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,16 +3928,19 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F61" s="3">
         <v>200</v>
@@ -3806,38 +3949,38 @@
         <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I61" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="K61" s="3">
         <v>300</v>
       </c>
       <c r="L61" s="3">
+        <v>300</v>
+      </c>
+      <c r="M61" s="3">
         <v>6300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3853,55 +3996,58 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -3918,8 +4064,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3983,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4048,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4113,56 +4268,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E66" s="3">
         <v>22200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>41200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>49600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4203,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4268,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4333,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4398,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4463,56 +4634,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-121700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-118200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-114700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-114000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-110300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-104800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-109900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-103700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-88000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-83100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-73500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-65700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-56000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-47100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-36400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4528,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4593,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4658,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4723,56 +4906,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3">
         <v>2700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-7900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-7500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-12500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-13600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-7100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-8900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4853,61 +5042,64 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4923,8 +5115,11 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4932,47 +5127,47 @@
         <v>-3500</v>
       </c>
       <c r="E81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4988,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5013,31 +5211,32 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>700</v>
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
@@ -5052,17 +5251,17 @@
         <v>600</v>
       </c>
       <c r="O83" s="3">
+        <v>600</v>
+      </c>
+      <c r="P83" s="3">
         <v>400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5078,8 +5277,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5143,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5208,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5273,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5338,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5403,56 +5617,59 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3500</v>
       </c>
-      <c r="H89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5493,8 +5713,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5513,11 +5734,11 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5537,8 +5758,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5552,14 +5773,17 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5623,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5688,17 +5915,20 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -5708,15 +5938,15 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7300</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -5724,19 +5954,19 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5747,14 +5977,17 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5778,31 +6011,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5843,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5908,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5973,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6038,56 +6281,59 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4200</v>
       </c>
-      <c r="H100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6103,31 +6349,34 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6168,56 +6417,59 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
-        <v>-1600</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6231,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="92">
   <si>
     <t>DBGI</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,62 +756,68 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,62 +830,68 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,62 +904,68 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F10" s="3">
         <v>1100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>500</v>
       </c>
       <c r="H10" s="3">
         <v>1700</v>
       </c>
       <c r="I10" s="3">
+        <v>500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K10" s="3">
         <v>2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-200</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +978,14 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,8 +1010,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1053,8 +1080,14 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,55 +1154,61 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>800</v>
+      </c>
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>700</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-10700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>15500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1180,31 +1219,37 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>800</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
@@ -1213,13 +1258,13 @@
         <v>800</v>
       </c>
       <c r="J15" s="3">
+        <v>700</v>
+      </c>
+      <c r="K15" s="3">
+        <v>800</v>
+      </c>
+      <c r="L15" s="3">
         <v>1000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>500</v>
-      </c>
-      <c r="L15" s="3">
-        <v>500</v>
       </c>
       <c r="M15" s="3">
         <v>500</v>
@@ -1228,23 +1273,23 @@
         <v>500</v>
       </c>
       <c r="O15" s="3">
+        <v>500</v>
+      </c>
+      <c r="P15" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q15" s="3">
         <v>600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>100</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1257,8 +1302,14 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,62 +1331,64 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F17" s="3">
         <v>4600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>16600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>13300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>9000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>13800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>10100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>11800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,62 +1401,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-13200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-10700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-9800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-10800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1475,14 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,61 +1507,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>700</v>
+      </c>
+      <c r="M20" s="3">
+        <v>400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>700</v>
-      </c>
-      <c r="K20" s="3">
-        <v>400</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="Q20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>3400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1510,62 +1577,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-6700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-7500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-10700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,62 +1651,68 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>3000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>2300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>2200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,62 +1725,68 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>6500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-15800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-9500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-9700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-11800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,37 +1799,43 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3">
+        <v>-100</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1759,16 +1850,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-1100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1776,14 +1867,20 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,62 +1947,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-5400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>6500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-15800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-10700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,62 +2021,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-5400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-15800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-10700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2095,14 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2169,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2075,31 +2196,31 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-1500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>100</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3">
         <v>-200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-100</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2122,8 +2243,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2317,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,61 +2391,67 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="Q32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R32" s="3">
+        <v>600</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="P32" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2326,62 +2465,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-15800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-10700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2539,14 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,62 +2613,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-15800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-10700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,67 +2687,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2766,14 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2798,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,62 +2826,64 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>1100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,8 +2896,14 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2791,40 +2970,46 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1100</v>
       </c>
       <c r="N43" s="3">
         <v>1000</v>
@@ -2833,20 +3018,20 @@
         <v>1100</v>
       </c>
       <c r="P43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,62 +3044,68 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F44" s="3">
         <v>5000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>4600</v>
-      </c>
-      <c r="G44" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H44" s="3">
-        <v>4700</v>
       </c>
       <c r="I44" s="3">
         <v>4800</v>
       </c>
       <c r="J44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L44" s="3">
         <v>4900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>600</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,8 +3118,14 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2953,36 +3150,36 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,62 +3192,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F46" s="3">
         <v>6400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1700</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3063,8 +3266,14 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3089,14 +3298,14 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>200</v>
-      </c>
-      <c r="L47" s="3">
-        <v>100</v>
-      </c>
-      <c r="M47" s="3">
-        <v>100</v>
       </c>
       <c r="N47" s="3">
         <v>100</v>
@@ -3105,19 +3314,19 @@
         <v>100</v>
       </c>
       <c r="P47" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q47" s="3">
         <v>100</v>
       </c>
       <c r="R47" s="3">
+        <v>200</v>
+      </c>
+      <c r="S47" s="3">
         <v>100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>100</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3131,49 +3340,55 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
         <v>400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>500</v>
       </c>
       <c r="G48" s="3">
         <v>700</v>
       </c>
       <c r="H48" s="3">
+        <v>500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>700</v>
+      </c>
+      <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>100</v>
-      </c>
-      <c r="P48" s="3">
-        <v>100</v>
       </c>
       <c r="Q48" s="3">
         <v>100</v>
@@ -3181,11 +3396,11 @@
       <c r="R48" s="3">
         <v>100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>100</v>
+      </c>
+      <c r="T48" s="3">
+        <v>100</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3199,62 +3414,68 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F49" s="3">
         <v>16300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>17500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>18200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>19000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>19700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>20400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>23600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>24500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>29500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>30000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>30600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>31100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>34600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>27300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>13900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3267,8 +3488,14 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3562,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,22 +3636,28 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -3430,13 +3669,13 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
@@ -3448,16 +3687,16 @@
         <v>400</v>
       </c>
       <c r="Q52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>400</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3471,8 +3710,14 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,62 +3784,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F54" s="3">
         <v>23300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>24900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>24800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>25300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>27700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>27600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>33100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>33700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>35000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>36400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>36000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>36500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>40700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>34000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>16200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3858,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3890,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,62 +3918,64 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="E57" s="3">
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="F57" s="3">
         <v>6300</v>
       </c>
       <c r="G57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I57" s="3">
         <v>7500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>8100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>7700</v>
       </c>
       <c r="K57" s="3">
         <v>8100</v>
       </c>
       <c r="L57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="M57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="N57" s="3">
         <v>6900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>6300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,62 +3988,68 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8900</v>
+        <v>5400</v>
       </c>
       <c r="E58" s="3">
-        <v>8400</v>
+        <v>6400</v>
       </c>
       <c r="F58" s="3">
         <v>8900</v>
       </c>
       <c r="G58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>8900</v>
+      </c>
+      <c r="I58" s="3">
         <v>8500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>13400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>13800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>13200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>11500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>13700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>12400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,62 +4062,68 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
       </c>
       <c r="G59" s="3">
+        <v>100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>100</v>
+      </c>
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>19000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>25400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>25500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>18700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>16100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>13700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>9400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,62 +4136,68 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F60" s="3">
         <v>22400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>21400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>21400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>22400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>22700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>40100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>40900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>45500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>44000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>40800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>35000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>23700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>21600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>15400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,62 +4210,68 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>200</v>
-      </c>
-      <c r="G61" s="3">
-        <v>200</v>
       </c>
       <c r="H61" s="3">
         <v>200</v>
       </c>
       <c r="I61" s="3">
+        <v>200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>200</v>
+      </c>
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>13000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3999,8 +4284,14 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4025,35 +4316,35 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>1700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
@@ -4067,8 +4358,14 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4432,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4506,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,62 +4580,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F66" s="3">
         <v>23300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>22200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>21900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>23700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>22500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>23100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>41000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>41200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>47500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>51300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>49600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>43600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>39200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>29100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>25000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4654,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4686,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4756,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4830,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4904,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,62 +4978,68 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-129200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-127100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-121700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-118200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-114700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-114000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-110300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-104800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-109900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-103700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-88000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-83100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-73500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-65700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-47100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-36400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +5052,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +5126,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5200,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,62 +5274,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="E76" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
         <v>2700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-7500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-12500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-14900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-13600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-7100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-8900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5348,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5422,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,62 +5501,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-15800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-10700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5575,14 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,22 +5607,24 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
+        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -5239,10 +5636,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>600</v>
@@ -5254,20 +5651,20 @@
         <v>600</v>
       </c>
       <c r="P83" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>600</v>
+      </c>
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5280,8 +5677,14 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5751,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5825,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5899,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5973,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,62 +6047,68 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3500</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5688,8 +6121,14 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,13 +6153,15 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -5734,17 +6175,17 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5761,11 +6202,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5776,14 +6217,20 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6297,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,61 +6371,67 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
+        <v>100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-7300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="P94" s="3">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="3">
         <v>-500</v>
       </c>
       <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+        <v>-5000</v>
+      </c>
+      <c r="S94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5980,14 +6439,20 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6477,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6038,11 +6505,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6080,8 +6547,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6621,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6695,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,62 +6769,68 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>4200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>10300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>6200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>3500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>8800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,8 +6843,14 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6378,11 +6875,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6420,62 +6917,68 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H102" s="3">
-        <v>700</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>700</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>700</v>
+      </c>
+      <c r="M102" s="3">
         <v>1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,6 +6989,12 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="92">
   <si>
     <t>DBGI</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -762,65 +763,68 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -836,64 +840,67 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1000</v>
-      </c>
-      <c r="S9" s="3">
-        <v>600</v>
       </c>
       <c r="T9" s="3">
         <v>600</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
+      <c r="U9" s="3">
+        <v>600</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
@@ -910,65 +917,68 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
         <v>900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1100</v>
       </c>
       <c r="P10" s="3">
         <v>1100</v>
       </c>
       <c r="Q10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R10" s="3">
         <v>1500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +994,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1012,8 +1025,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1086,8 +1100,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,58 +1177,61 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-10700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>15500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>3000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1225,8 +1245,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1234,8 +1254,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1246,28 +1269,28 @@
         <v>400</v>
       </c>
       <c r="F15" s="3">
+        <v>400</v>
+      </c>
+      <c r="G15" s="3">
         <v>600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>700</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
       </c>
       <c r="I15" s="3">
+        <v>700</v>
+      </c>
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>500</v>
       </c>
       <c r="N15" s="3">
         <v>500</v>
@@ -1279,20 +1302,20 @@
         <v>500</v>
       </c>
       <c r="Q15" s="3">
+        <v>500</v>
+      </c>
+      <c r="R15" s="3">
         <v>600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>100</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,8 +1331,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1333,65 +1359,66 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1407,8 +1434,11 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1416,56 +1446,56 @@
         <v>-2000</v>
       </c>
       <c r="E18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,8 +1511,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1509,8 +1542,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1518,13 +1552,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1533,40 +1567,40 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1583,65 +1617,68 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-1600</v>
       </c>
       <c r="G21" s="3">
         <v>-1600</v>
       </c>
       <c r="H21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I21" s="3">
         <v>500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,8 +1694,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1666,56 +1706,56 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1600</v>
       </c>
       <c r="Q22" s="3">
         <v>1600</v>
       </c>
       <c r="R22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1731,8 +1771,11 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1740,56 +1783,56 @@
         <v>-2100</v>
       </c>
       <c r="E23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-3500</v>
       </c>
       <c r="G23" s="3">
         <v>-3500</v>
       </c>
       <c r="H23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,40 +1848,43 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1856,13 +1902,13 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-1100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1873,14 +1919,17 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1953,8 +2002,11 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1962,56 +2014,56 @@
         <v>-2100</v>
       </c>
       <c r="E26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5400</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-3500</v>
       </c>
       <c r="G26" s="3">
         <v>-3500</v>
       </c>
       <c r="H26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,8 +2079,11 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2036,56 +2091,56 @@
         <v>-2100</v>
       </c>
       <c r="E27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-3500</v>
       </c>
       <c r="G27" s="3">
         <v>-3500</v>
       </c>
       <c r="H27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2101,8 +2156,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2175,8 +2233,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2202,28 +2263,28 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>100</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3">
         <v>-200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2249,8 +2310,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2323,8 +2387,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2397,8 +2464,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2406,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -2421,40 +2491,40 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2541,11 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2480,56 +2553,56 @@
         <v>-2100</v>
       </c>
       <c r="E33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-3500</v>
       </c>
       <c r="G33" s="3">
         <v>-3500</v>
       </c>
       <c r="H33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2618,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2619,8 +2695,11 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2628,56 +2707,56 @@
         <v>-2100</v>
       </c>
       <c r="E35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-3500</v>
       </c>
       <c r="G35" s="3">
         <v>-3500</v>
       </c>
       <c r="H35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,70 +2772,73 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2854,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2800,8 +2885,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2828,65 +2914,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>1100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,8 +2989,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2976,65 +3066,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E43" s="3">
         <v>400</v>
       </c>
       <c r="F43" s="3">
+        <v>400</v>
+      </c>
+      <c r="G43" s="3">
         <v>700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1000</v>
       </c>
       <c r="H43" s="3">
         <v>1000</v>
       </c>
       <c r="I43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3050,65 +3143,68 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E44" s="3">
         <v>4300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>600</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3124,16 +3220,19 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="E45" s="3">
+        <v>5400</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -3156,33 +3255,33 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>900</v>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N45" s="3">
         <v>900</v>
       </c>
       <c r="O45" s="3">
+        <v>900</v>
+      </c>
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3198,65 +3297,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E46" s="3">
         <v>12500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1700</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3272,8 +3374,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3304,11 +3409,11 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>200</v>
-      </c>
-      <c r="N47" s="3">
-        <v>100</v>
       </c>
       <c r="O47" s="3">
         <v>100</v>
@@ -3320,16 +3425,16 @@
         <v>100</v>
       </c>
       <c r="R47" s="3">
+        <v>100</v>
+      </c>
+      <c r="S47" s="3">
         <v>200</v>
-      </c>
-      <c r="S47" s="3">
-        <v>100</v>
       </c>
       <c r="T47" s="3">
         <v>100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>100</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3346,8 +3451,11 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3358,40 +3466,40 @@
         <v>0</v>
       </c>
       <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
       </c>
       <c r="Q48" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>100</v>
@@ -3402,8 +3510,8 @@
       <c r="T48" s="3">
         <v>100</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>100</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3420,65 +3528,68 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E49" s="3">
         <v>14700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>20400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>24500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>30000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>27300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13900</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3494,8 +3605,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3568,8 +3682,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3642,25 +3759,28 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>4100</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -3675,10 +3795,10 @@
         <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
@@ -3693,14 +3813,14 @@
         <v>400</v>
       </c>
       <c r="S52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3716,8 +3836,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3790,65 +3913,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E54" s="3">
         <v>27200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>24800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3990,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3892,8 +4021,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3920,65 +4050,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,65 +4125,68 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="E58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F58" s="3">
         <v>6400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,19 +4202,22 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>100</v>
       </c>
       <c r="G59" s="3">
         <v>100</v>
@@ -4089,44 +4226,44 @@
         <v>100</v>
       </c>
       <c r="I59" s="3">
+        <v>100</v>
+      </c>
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4142,65 +4279,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E60" s="3">
         <v>19700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>21400</v>
       </c>
       <c r="H60" s="3">
         <v>21400</v>
       </c>
       <c r="I60" s="3">
+        <v>21400</v>
+      </c>
+      <c r="J60" s="3">
         <v>23200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>45500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>44000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>35000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15400</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4356,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4225,16 +4368,16 @@
         <v>1100</v>
       </c>
       <c r="E61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>200</v>
       </c>
       <c r="I61" s="3">
         <v>200</v>
@@ -4243,38 +4386,38 @@
         <v>200</v>
       </c>
       <c r="K61" s="3">
+        <v>200</v>
+      </c>
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>900</v>
-      </c>
-      <c r="M61" s="3">
-        <v>300</v>
       </c>
       <c r="N61" s="3">
         <v>300</v>
       </c>
       <c r="O61" s="3">
+        <v>300</v>
+      </c>
+      <c r="P61" s="3">
         <v>6300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4290,8 +4433,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4322,32 +4468,32 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -4364,8 +4510,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4438,8 +4587,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4512,8 +4664,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4586,65 +4741,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E66" s="3">
         <v>21000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>41000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>49600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>43600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>39200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4818,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4688,8 +4849,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4762,8 +4924,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4836,8 +5001,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4910,8 +5078,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4984,65 +5155,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-131300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-129200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-127100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-121700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-118200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-114700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-114000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-110300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-104800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-109900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-103700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-88000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-83100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-73500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-65700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-56000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-47100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-36400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5058,8 +5232,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5132,8 +5309,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5206,8 +5386,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5280,65 +5463,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1300</v>
       </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
       <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
         <v>2700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-7900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-7500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-12500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-14900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-7100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-8900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5354,8 +5540,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5428,70 +5617,73 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5507,8 +5699,11 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5516,56 +5711,56 @@
         <v>-2100</v>
       </c>
       <c r="E81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-3500</v>
       </c>
       <c r="G81" s="3">
         <v>-3500</v>
       </c>
       <c r="H81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5581,8 +5776,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5609,25 +5807,26 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -5642,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>600</v>
@@ -5657,17 +5856,17 @@
         <v>600</v>
       </c>
       <c r="R83" s="3">
+        <v>600</v>
+      </c>
+      <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5683,8 +5882,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5757,8 +5959,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5831,8 +6036,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5905,8 +6113,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5979,8 +6190,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6053,65 +6267,68 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6127,8 +6344,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6155,16 +6375,17 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -6181,14 +6402,14 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6208,8 +6429,8 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -6223,14 +6444,17 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6303,8 +6527,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6377,22 +6604,25 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -6403,18 +6633,18 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -6422,19 +6652,19 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6445,14 +6675,17 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6479,8 +6712,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6511,8 +6745,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6553,8 +6787,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6627,8 +6864,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6701,8 +6941,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6775,65 +7018,68 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>6600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6849,8 +7095,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6881,8 +7130,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6923,65 +7172,68 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>700</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6995,6 +7247,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DBGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="92">
   <si>
     <t>DBGI</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -770,74 +771,80 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>400</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -850,74 +857,80 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F9" s="3">
         <v>900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>600</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -930,74 +943,80 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1600</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K10" s="3">
-        <v>500</v>
       </c>
       <c r="L10" s="3">
         <v>1700</v>
       </c>
       <c r="M10" s="3">
+        <v>500</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O10" s="3">
         <v>2300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-200</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,8 +1029,14 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,8 +1065,10 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1120,8 +1147,14 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,67 +1233,73 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>5700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-10700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>15500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1271,25 +1310,31 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
@@ -1298,16 +1343,16 @@
         <v>400</v>
       </c>
       <c r="H15" s="3">
+        <v>400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>400</v>
+      </c>
+      <c r="J15" s="3">
         <v>600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>800</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
@@ -1316,13 +1361,13 @@
         <v>800</v>
       </c>
       <c r="N15" s="3">
+        <v>700</v>
+      </c>
+      <c r="O15" s="3">
+        <v>800</v>
+      </c>
+      <c r="P15" s="3">
         <v>1000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>500</v>
-      </c>
-      <c r="P15" s="3">
-        <v>500</v>
       </c>
       <c r="Q15" s="3">
         <v>500</v>
@@ -1331,23 +1376,23 @@
         <v>500</v>
       </c>
       <c r="S15" s="3">
+        <v>500</v>
+      </c>
+      <c r="T15" s="3">
+        <v>500</v>
+      </c>
+      <c r="U15" s="3">
         <v>600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>100</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,8 +1405,14 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1387,74 +1438,76 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F17" s="3">
         <v>5000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>8100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>16600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>13300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>9000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>10100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>11800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,74 +1520,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-13200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-10700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-9800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-7900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-10800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1606,14 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1577,73 +1642,75 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1657,74 +1724,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-12300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-6700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-7500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-8100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-10700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2200</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1810,14 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1752,59 +1831,59 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
+        <v>100</v>
+      </c>
+      <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>2200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>700</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,74 +1896,80 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-15800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-9500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-7800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-9700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-8900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-11800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1897,8 +1982,14 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1911,35 +2002,35 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1954,16 +2045,16 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-1100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
@@ -1971,14 +2062,20 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2057,74 +2154,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>6500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-15800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-9500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-7800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-9700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-8900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-10700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2137,74 +2240,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-15800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-9500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-7800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-9700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-8900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-10700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,8 +2326,14 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2297,8 +2412,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2330,31 +2451,31 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-1500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>100</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2377,8 +2498,14 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2457,8 +2584,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2537,73 +2670,79 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-3800</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2617,74 +2756,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-5400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-15800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-7800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-9700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-8900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-10700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,8 +2842,14 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2777,74 +2928,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-5400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-15800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-7800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-9700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-8900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-10700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,79 +3014,85 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2942,8 +3105,14 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2972,8 +3141,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3002,74 +3173,76 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F41" s="3">
         <v>6700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>1100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3082,8 +3255,14 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3162,52 +3341,58 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1500</v>
-      </c>
-      <c r="P43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1100</v>
       </c>
       <c r="R43" s="3">
         <v>1000</v>
@@ -3216,20 +3401,20 @@
         <v>1100</v>
       </c>
       <c r="T43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3242,74 +3427,80 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4300</v>
+        <v>3500</v>
       </c>
       <c r="E44" s="3">
-        <v>4100</v>
+        <v>3100</v>
       </c>
       <c r="F44" s="3">
         <v>4300</v>
       </c>
       <c r="G44" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I44" s="3">
         <v>3800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>4600</v>
-      </c>
-      <c r="K44" s="3">
-        <v>4800</v>
-      </c>
-      <c r="L44" s="3">
-        <v>4700</v>
       </c>
       <c r="M44" s="3">
         <v>4800</v>
       </c>
       <c r="N44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="P44" s="3">
         <v>4900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>5200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>600</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3322,8 +3513,14 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3333,15 +3530,15 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>5400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3360,36 +3557,36 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3402,74 +3599,80 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F46" s="3">
         <v>20000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>8900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>6400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1700</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3685,14 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3520,14 +3729,14 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>200</v>
-      </c>
-      <c r="P47" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>100</v>
       </c>
       <c r="R47" s="3">
         <v>100</v>
@@ -3536,19 +3745,19 @@
         <v>100</v>
       </c>
       <c r="T47" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U47" s="3">
         <v>100</v>
       </c>
       <c r="V47" s="3">
+        <v>200</v>
+      </c>
+      <c r="W47" s="3">
         <v>100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>100</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
@@ -3562,13 +3771,19 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
@@ -3580,43 +3795,43 @@
         <v>0</v>
       </c>
       <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
         <v>400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>500</v>
       </c>
       <c r="K48" s="3">
         <v>700</v>
       </c>
       <c r="L48" s="3">
+        <v>500</v>
+      </c>
+      <c r="M48" s="3">
+        <v>700</v>
+      </c>
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>300</v>
-      </c>
-      <c r="S48" s="3">
-        <v>100</v>
-      </c>
-      <c r="T48" s="3">
-        <v>100</v>
       </c>
       <c r="U48" s="3">
         <v>100</v>
@@ -3624,11 +3839,11 @@
       <c r="V48" s="3">
         <v>100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>100</v>
+      </c>
+      <c r="X48" s="3">
+        <v>100</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3642,74 +3857,80 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F49" s="3">
         <v>16800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>17300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>14700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>15100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>16300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>17500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>18200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>19000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>19700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>20400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>23600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>24500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>29500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>30000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>30600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>31100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>34600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>27300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>13900</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,8 +3943,14 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3802,8 +4029,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3882,34 +4115,40 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F52" s="3">
         <v>4300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -3921,13 +4160,13 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
@@ -3939,16 +4178,16 @@
         <v>400</v>
       </c>
       <c r="U52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>400</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -3962,8 +4201,14 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4042,74 +4287,80 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F54" s="3">
         <v>41200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>27800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>27200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>23300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>24900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>24800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>25300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>27700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>27600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>33100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>33700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>36400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>36000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>36500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>40700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>34000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>16200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4122,8 +4373,14 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4152,8 +4409,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4182,74 +4441,76 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>6300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>6100</v>
       </c>
       <c r="J57" s="3">
         <v>6300</v>
       </c>
       <c r="K57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="L57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M57" s="3">
         <v>7500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>8100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>7700</v>
       </c>
       <c r="O57" s="3">
         <v>8100</v>
       </c>
       <c r="P57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="R57" s="3">
         <v>6900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>7000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>8500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>6600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>6900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>6300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>6000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4262,74 +4523,80 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F58" s="3">
         <v>6200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>6400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>8900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>8400</v>
       </c>
       <c r="J58" s="3">
         <v>8900</v>
       </c>
       <c r="K58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="L58" s="3">
+        <v>8900</v>
+      </c>
+      <c r="M58" s="3">
         <v>8500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>13400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>13800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>13200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>11500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>13700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>12400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>6600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,74 +4609,80 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F59" s="3">
         <v>5700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
-        <v>500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>100</v>
+      </c>
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>12900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>19000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>25400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>25500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>18700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>16100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>13700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>9400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4422,74 +4695,80 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F60" s="3">
         <v>24800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>19400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>19700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>20800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>22400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>21400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>21400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>23200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>22400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>22700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>40100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>40900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>45500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>44000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>40800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>35000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>23700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>21600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>15400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,74 +4781,80 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>200</v>
-      </c>
-      <c r="K61" s="3">
-        <v>200</v>
       </c>
       <c r="L61" s="3">
         <v>200</v>
       </c>
       <c r="M61" s="3">
+        <v>200</v>
+      </c>
+      <c r="N61" s="3">
+        <v>200</v>
+      </c>
+      <c r="O61" s="3">
         <v>500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>6300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>6200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>13000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>7500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>9600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4582,16 +4867,22 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9400</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -4620,35 +4911,35 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>1700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
@@ -4662,8 +4953,14 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4742,8 +5039,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4822,8 +5125,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4902,74 +5211,80 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>35700</v>
+      </c>
+      <c r="F66" s="3">
         <v>25200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>20700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>21000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>21200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>23300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>22200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>21900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>23700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>22500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>23100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>41000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>41200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>47500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>51300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>49600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>43600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>39200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>29100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>25000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,8 +5297,14 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5012,8 +5333,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5092,8 +5415,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5172,8 +5501,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5252,8 +5587,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5332,74 +5673,80 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-166700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-155400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-134800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-131300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-129200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-127100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-121700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-118200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-114700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-114000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-110300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-104800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-109900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-103700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-83100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-73500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-65700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-56000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-47100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-36400</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,8 +5759,14 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5492,8 +5845,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5572,8 +5931,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5652,74 +6017,80 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F76" s="3">
         <v>16000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1300</v>
       </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3">
         <v>2700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-7900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-7500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-14900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-13600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-7100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-8900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5732,8 +6103,14 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5812,79 +6189,85 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5897,74 +6280,80 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-5400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-15800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-7800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-9700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-8900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-10700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,8 +6366,14 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6007,34 +6402,36 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -6046,10 +6443,10 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>600</v>
@@ -6061,20 +6458,20 @@
         <v>600</v>
       </c>
       <c r="T83" s="3">
+        <v>600</v>
+      </c>
+      <c r="U83" s="3">
+        <v>600</v>
+      </c>
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6087,8 +6484,14 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6167,8 +6570,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6247,8 +6656,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6327,8 +6742,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6407,8 +6828,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6487,74 +6914,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4500</v>
       </c>
-      <c r="G89" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-6000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6567,8 +7000,14 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6597,13 +7036,15 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>3</v>
@@ -6611,11 +7052,11 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -6629,17 +7070,17 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6656,11 +7097,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6671,14 +7112,20 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6757,8 +7204,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6837,13 +7290,19 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-300</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
@@ -6851,59 +7310,59 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
-        <v>100</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-7300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="T94" s="3">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>-500</v>
       </c>
       <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+        <v>-5000</v>
+      </c>
+      <c r="W94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -6911,14 +7370,20 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6947,8 +7412,10 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6985,11 +7452,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7027,8 +7494,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7107,8 +7580,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7666,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7267,74 +7752,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>16900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>6600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>4200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>10300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>6200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>6100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>8800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7347,8 +7838,14 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7385,11 +7882,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7427,74 +7924,80 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F102" s="3">
         <v>11900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1100</v>
-      </c>
-      <c r="L102" s="3">
-        <v>700</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
       </c>
       <c r="N102" s="3">
         <v>700</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q102" s="3">
         <v>1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7505,6 +8008,12 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
